--- a/artfynd/A 63116-2025 artfynd.xlsx
+++ b/artfynd/A 63116-2025 artfynd.xlsx
@@ -879,7 +879,7 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>

--- a/artfynd/A 63116-2025 artfynd.xlsx
+++ b/artfynd/A 63116-2025 artfynd.xlsx
@@ -675,55 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120354479</v>
+        <v>120357670</v>
       </c>
       <c r="B2" t="n">
-        <v>8421</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Östra Låsberget, Östra Låsberget, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496609</v>
+        <v>496562</v>
       </c>
       <c r="R2" t="n">
-        <v>6670538</v>
+        <v>6670519</v>
       </c>
       <c r="S2" t="n">
         <v>9</v>
@@ -755,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,14 +755,14 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="b">
         <v>0</v>
@@ -785,52 +775,57 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars-Ove Wikars, Bo karlstens</t>
+          <t>Bo karlstens, Lars-Ove Wikars</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120357670</v>
+        <v>120354479</v>
       </c>
       <c r="B3" t="n">
-        <v>79120</v>
+        <v>8444</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Östra Låsberget, Östra Låsberget, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496562</v>
+        <v>496609</v>
       </c>
       <c r="R3" t="n">
-        <v>6670519</v>
+        <v>6670538</v>
       </c>
       <c r="S3" t="n">
         <v>9</v>
@@ -862,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,14 +867,14 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
@@ -892,7 +887,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Bo karlstens, Lars-Ove Wikars</t>
+          <t>Lars-Ove Wikars, Bo karlstens</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
